--- a/outputs/llm_eval/topical_yjx/sig/General_Public_correlation_results.xlsx
+++ b/outputs/llm_eval/topical_yjx/sig/General_Public_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.2585014768121828</v>
+        <v>0.4582931159114899</v>
       </c>
       <c r="C2">
-        <v>0.2699079759573071</v>
+        <v>0.4468469457735034</v>
       </c>
       <c r="D2">
-        <v>0.2149850802531933</v>
+        <v>0.4021028067815282</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.2461035660129727</v>
+        <v>0.4291100644984099</v>
       </c>
       <c r="C3">
-        <v>0.2726619248219863</v>
+        <v>0.4177985401031094</v>
       </c>
       <c r="D3">
-        <v>0.2109103118923854</v>
+        <v>0.3940566090462832</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,18 +445,27 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.4577051694295863</v>
+        <v>0.588375479741657</v>
       </c>
       <c r="C4">
-        <v>0.4658249618998446</v>
+        <v>0.5867561585481321</v>
       </c>
       <c r="D4">
-        <v>0.3883303949450005</v>
+        <v>0.5420098417092493</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0.5699412375245206</v>
+      </c>
+      <c r="C5">
+        <v>0.576113914756083</v>
+      </c>
+      <c r="D5">
+        <v>0.5558275694506465</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/llm_eval/topical_yjx/sig/General_Public_correlation_results.xlsx
+++ b/outputs/llm_eval/topical_yjx/sig/General_Public_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.4582931159114899</v>
+        <v>0.495843665316499</v>
       </c>
       <c r="C2">
-        <v>0.4468469457735034</v>
+        <v>0.4743096593137602</v>
       </c>
       <c r="D2">
-        <v>0.4021028067815282</v>
+        <v>0.4436562691456575</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.4291100644984099</v>
+        <v>0.5449965821692814</v>
       </c>
       <c r="C3">
-        <v>0.4177985401031094</v>
+        <v>0.5264658789572454</v>
       </c>
       <c r="D3">
-        <v>0.3940566090462832</v>
+        <v>0.5008238337599569</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.588375479741657</v>
+        <v>0.6138305811734283</v>
       </c>
       <c r="C4">
-        <v>0.5867561585481321</v>
+        <v>0.6054706029030607</v>
       </c>
       <c r="D4">
-        <v>0.5420098417092493</v>
+        <v>0.5638437546628182</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.5699412375245206</v>
+        <v>0.5952882130219839</v>
       </c>
       <c r="C5">
-        <v>0.576113914756083</v>
+        <v>0.6180545563822454</v>
       </c>
       <c r="D5">
-        <v>0.5558275694506465</v>
+        <v>0.5762981307173066</v>
       </c>
     </row>
   </sheetData>
